--- a/erp-server/erp-server-file/src/main/resources/excel/oms/fullyManagedOrder.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/fullyManagedOrder.xlsx
@@ -114,10 +114,10 @@
     <t>实际发货时间</t>
   </si>
   <si>
+    <t>平台SKU</t>
+  </si>
+  <si>
     <t>平台SKU货号</t>
-  </si>
-  <si>
-    <t>平台SKU</t>
   </si>
   <si>
     <t>SKU</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/fullyManagedOrder.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/fullyManagedOrder.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
   <si>
     <t>销售单号</t>
   </si>
@@ -144,13 +144,6 @@
     <t>含税成本+币种</t>
   </si>
   <si>
-    <t>订单金额原始币种</t>
-  </si>
-  <si>
-    <t xml:space="preserve">订单金额人民币
-</t>
-  </si>
-  <si>
     <t>成本来源</t>
   </si>
   <si>
@@ -272,12 +265,6 @@
   </si>
   <si>
     <t>{.taxCost}/CNY</t>
-  </si>
-  <si>
-    <t>{.sourceAmount}</t>
-  </si>
-  <si>
-    <t>{.baseAmount}</t>
   </si>
   <si>
     <t>{.costSource}</t>
@@ -1223,7 +1210,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AX2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1256,23 +1243,21 @@
     <col min="33" max="33" width="17.375" customWidth="1"/>
     <col min="34" max="36" width="17.75" customWidth="1"/>
     <col min="37" max="37" width="32.75" customWidth="1"/>
-    <col min="38" max="38" width="15.875" customWidth="1"/>
-    <col min="39" max="39" width="15" customWidth="1"/>
-    <col min="40" max="40" width="17.375" customWidth="1"/>
-    <col min="41" max="41" width="14.375" customWidth="1"/>
-    <col min="42" max="42" width="18.125" customWidth="1"/>
-    <col min="43" max="43" width="15.25" customWidth="1"/>
-    <col min="44" max="44" width="17" customWidth="1"/>
-    <col min="45" max="45" width="15.75" customWidth="1"/>
-    <col min="46" max="46" width="14.625" customWidth="1"/>
-    <col min="47" max="47" width="14.125" customWidth="1"/>
-    <col min="48" max="48" width="17.375" customWidth="1"/>
-    <col min="49" max="49" width="17.25" customWidth="1"/>
-    <col min="50" max="50" width="15.625" customWidth="1"/>
-    <col min="51" max="51" width="13.625" customWidth="1"/>
+    <col min="38" max="38" width="17.375" customWidth="1"/>
+    <col min="39" max="39" width="14.375" customWidth="1"/>
+    <col min="40" max="40" width="18.125" customWidth="1"/>
+    <col min="41" max="41" width="15.25" customWidth="1"/>
+    <col min="42" max="42" width="17" customWidth="1"/>
+    <col min="43" max="43" width="15.75" customWidth="1"/>
+    <col min="44" max="44" width="14.625" customWidth="1"/>
+    <col min="45" max="45" width="14.125" customWidth="1"/>
+    <col min="46" max="46" width="17.375" customWidth="1"/>
+    <col min="47" max="47" width="17.25" customWidth="1"/>
+    <col min="48" max="48" width="15.625" customWidth="1"/>
+    <col min="49" max="49" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:52">
+    <row r="1" ht="40.5" spans="1:50">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1384,24 +1369,20 @@
       <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" t="s">
         <v>37</v>
       </c>
       <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>42</v>
-      </c>
+      <c r="AP1" s="1"/>
+      <c r="AQ1" s="1"/>
       <c r="AR1" s="1"/>
       <c r="AS1" s="1"/>
       <c r="AT1" s="1"/>
@@ -1409,138 +1390,130 @@
       <c r="AV1" s="1"/>
       <c r="AW1" s="1"/>
       <c r="AX1" s="1"/>
-      <c r="AY1" s="1"/>
-      <c r="AZ1" s="1"/>
     </row>
-    <row r="2" spans="1:43">
+    <row r="2" spans="1:41">
       <c r="A2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" t="s">
         <v>43</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>44</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>45</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>46</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>47</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>48</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>49</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>50</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>51</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>52</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>53</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>54</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>55</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>56</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>57</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>58</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>59</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>60</v>
       </c>
-      <c r="S2" t="s">
+      <c r="U2" t="s">
         <v>61</v>
       </c>
-      <c r="T2" t="s">
+      <c r="V2" t="s">
         <v>62</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>63</v>
       </c>
-      <c r="V2" t="s">
+      <c r="X2" t="s">
         <v>64</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Y2" t="s">
         <v>65</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>66</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
         <v>67</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>68</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AC2" t="s">
         <v>69</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AD2" t="s">
         <v>70</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AE2" t="s">
         <v>71</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AF2" t="s">
         <v>72</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AG2" t="s">
         <v>73</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AH2" t="s">
         <v>74</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AI2" t="s">
         <v>75</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AJ2" t="s">
         <v>76</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AK2" t="s">
         <v>77</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AL2" t="s">
         <v>78</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AM2" t="s">
         <v>79</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AN2" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AO2" t="s">
         <v>81</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/fullyManagedOrder.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/fullyManagedOrder.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>销售单号</t>
   </si>
@@ -54,6 +54,12 @@
   </si>
   <si>
     <t>订单创建时间</t>
+  </si>
+  <si>
+    <t>创建人</t>
+  </si>
+  <si>
+    <t>审核人</t>
   </si>
   <si>
     <t>下单时间</t>
@@ -181,6 +187,12 @@
   </si>
   <si>
     <t>{.createTime}</t>
+  </si>
+  <si>
+    <t>{.createUserName}</t>
+  </si>
+  <si>
+    <t>{.approveUserName}</t>
   </si>
   <si>
     <t>{.payTime}</t>
@@ -1210,7 +1222,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1221,43 +1233,45 @@
     <col min="7" max="7" width="13.75" customWidth="1"/>
     <col min="9" max="9" width="17.375" customWidth="1"/>
     <col min="10" max="10" width="13.875" customWidth="1"/>
-    <col min="11" max="11" width="17.375" customWidth="1"/>
-    <col min="12" max="13" width="22.125" customWidth="1"/>
-    <col min="14" max="14" width="13.375" customWidth="1"/>
-    <col min="15" max="15" width="14.125" customWidth="1"/>
-    <col min="17" max="17" width="11.375" customWidth="1"/>
-    <col min="18" max="18" width="10.5" customWidth="1"/>
-    <col min="19" max="19" width="11.125" customWidth="1"/>
-    <col min="20" max="20" width="15" customWidth="1"/>
-    <col min="21" max="21" width="17.625" customWidth="1"/>
-    <col min="22" max="22" width="12" customWidth="1"/>
-    <col min="23" max="23" width="12.375" customWidth="1"/>
-    <col min="24" max="24" width="10.375" customWidth="1"/>
-    <col min="25" max="25" width="15" customWidth="1"/>
-    <col min="26" max="26" width="18.625" customWidth="1"/>
-    <col min="27" max="27" width="14.625" customWidth="1"/>
-    <col min="28" max="28" width="16.5" customWidth="1"/>
-    <col min="29" max="29" width="17.875" customWidth="1"/>
-    <col min="30" max="31" width="14.25" customWidth="1"/>
-    <col min="32" max="32" width="12.75" customWidth="1"/>
-    <col min="33" max="33" width="17.375" customWidth="1"/>
-    <col min="34" max="36" width="17.75" customWidth="1"/>
-    <col min="37" max="37" width="32.75" customWidth="1"/>
-    <col min="38" max="38" width="17.375" customWidth="1"/>
-    <col min="39" max="39" width="14.375" customWidth="1"/>
-    <col min="40" max="40" width="18.125" customWidth="1"/>
-    <col min="41" max="41" width="15.25" customWidth="1"/>
-    <col min="42" max="42" width="17" customWidth="1"/>
-    <col min="43" max="43" width="15.75" customWidth="1"/>
-    <col min="44" max="44" width="14.625" customWidth="1"/>
-    <col min="45" max="45" width="14.125" customWidth="1"/>
-    <col min="46" max="46" width="17.375" customWidth="1"/>
-    <col min="47" max="47" width="17.25" customWidth="1"/>
-    <col min="48" max="48" width="15.625" customWidth="1"/>
-    <col min="49" max="49" width="13.625" customWidth="1"/>
+    <col min="11" max="11" width="15.25" customWidth="1"/>
+    <col min="12" max="12" width="13.875" customWidth="1"/>
+    <col min="13" max="13" width="17.375" customWidth="1"/>
+    <col min="14" max="15" width="22.125" customWidth="1"/>
+    <col min="16" max="16" width="13.375" customWidth="1"/>
+    <col min="17" max="17" width="14.125" customWidth="1"/>
+    <col min="19" max="19" width="11.375" customWidth="1"/>
+    <col min="20" max="20" width="10.5" customWidth="1"/>
+    <col min="21" max="21" width="11.125" customWidth="1"/>
+    <col min="22" max="22" width="15" customWidth="1"/>
+    <col min="23" max="23" width="17.625" customWidth="1"/>
+    <col min="24" max="24" width="12" customWidth="1"/>
+    <col min="25" max="25" width="12.375" customWidth="1"/>
+    <col min="26" max="26" width="10.375" customWidth="1"/>
+    <col min="27" max="27" width="15" customWidth="1"/>
+    <col min="28" max="28" width="18.625" customWidth="1"/>
+    <col min="29" max="29" width="14.625" customWidth="1"/>
+    <col min="30" max="30" width="16.5" customWidth="1"/>
+    <col min="31" max="31" width="17.875" customWidth="1"/>
+    <col min="32" max="33" width="14.25" customWidth="1"/>
+    <col min="34" max="34" width="12.75" customWidth="1"/>
+    <col min="35" max="35" width="17.375" customWidth="1"/>
+    <col min="36" max="38" width="17.75" customWidth="1"/>
+    <col min="39" max="39" width="32.75" customWidth="1"/>
+    <col min="40" max="40" width="17.375" customWidth="1"/>
+    <col min="41" max="41" width="14.375" customWidth="1"/>
+    <col min="42" max="42" width="18.125" customWidth="1"/>
+    <col min="43" max="43" width="15.25" customWidth="1"/>
+    <col min="44" max="44" width="17" customWidth="1"/>
+    <col min="45" max="45" width="15.75" customWidth="1"/>
+    <col min="46" max="46" width="14.625" customWidth="1"/>
+    <col min="47" max="47" width="14.125" customWidth="1"/>
+    <col min="48" max="48" width="17.375" customWidth="1"/>
+    <col min="49" max="49" width="17.25" customWidth="1"/>
+    <col min="50" max="50" width="15.625" customWidth="1"/>
+    <col min="51" max="51" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:50">
+    <row r="1" ht="40.5" spans="1:52">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1297,7 +1311,7 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
       <c r="O1" t="s">
@@ -1306,7 +1320,7 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
@@ -1315,10 +1329,10 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="V1" t="s">
@@ -1366,7 +1380,7 @@
       <c r="AJ1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" t="s">
         <v>36</v>
       </c>
       <c r="AL1" t="s">
@@ -1375,14 +1389,18 @@
       <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1"/>
-      <c r="AQ1" s="1"/>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>42</v>
+      </c>
       <c r="AR1" s="1"/>
       <c r="AS1" s="1"/>
       <c r="AT1" s="1"/>
@@ -1390,130 +1408,138 @@
       <c r="AV1" s="1"/>
       <c r="AW1" s="1"/>
       <c r="AX1" s="1"/>
+      <c r="AY1" s="1"/>
+      <c r="AZ1" s="1"/>
     </row>
-    <row r="2" spans="1:41">
+    <row r="2" spans="1:43">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="P2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Q2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="R2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="S2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="W2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="X2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Y2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AA2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AB2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AC2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AD2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AE2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AF2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AG2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="AH2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AI2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AJ2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AK2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AL2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AM2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AN2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AO2" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
